--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 121 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 119 clubs short</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>0</v>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3574,8 +3574,8 @@
       <c r="S28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T28" s="9" t="n">
-        <v>0</v>
+      <c r="T28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U28" s="9" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3971,13 +3971,13 @@
         </is>
       </c>
       <c r="P32" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="Q32" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="10" t="n">
         <v>2</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>1</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5432,8 +5432,8 @@
       <c r="S46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U46" s="9" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q64" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13616,8 +13616,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P126" s="9" t="n">
-        <v>3</v>
+      <c r="P126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q126" s="10" t="n">
         <v>2</v>
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13949,8 +13949,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -15560,7 +15560,7 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -19597,7 +19597,7 @@
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19667,8 +19667,8 @@
       <c r="Y185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z185" s="9" t="n">
-        <v>0</v>
+      <c r="Z185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA185" s="10" t="n">
         <v>1</v>
@@ -20003,7 +20003,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -20036,13 +20036,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -20168,7 +20168,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -20267,7 +20267,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -20663,7 +20663,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -20696,7 +20696,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -21092,7 +21092,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>

--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,11 @@
       <c r="AB8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1957,7 +1961,11 @@
       <c r="AB12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2365,7 +2373,11 @@
       <c r="AB16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3294,7 +3306,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3601,7 +3617,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4009,7 +4029,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -5051,7 +5075,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5152,7 +5180,11 @@
       <c r="AB43" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC43" s="4" t="inlineStr"/>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -6905,7 +6937,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7931,7 +7967,11 @@
       <c r="AB70" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -8339,7 +8379,11 @@
       <c r="AB74" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8440,7 +8484,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8541,7 +8589,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -9159,7 +9211,11 @@
       <c r="AB82" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC82" s="4" t="inlineStr"/>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9571,7 +9627,11 @@
       <c r="AB86" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -11619,7 +11679,11 @@
       <c r="AB106" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -12027,7 +12091,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12742,7 +12810,11 @@
       <c r="AB117" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC117" s="4" t="inlineStr"/>
+      <c r="AC117" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -12944,7 +13016,11 @@
       <c r="AB119" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC119" s="4" t="inlineStr"/>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -13554,7 +13630,11 @@
       <c r="AB125" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC125" s="4" t="inlineStr"/>
+      <c r="AC125" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13756,7 +13836,11 @@
       <c r="AB127" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC127" s="4" t="inlineStr"/>
+      <c r="AC127" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -14063,7 +14147,11 @@
       <c r="AB130" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr"/>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14265,7 +14353,11 @@
       <c r="AB132" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC132" s="4" t="inlineStr"/>
+      <c r="AC132" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -14572,7 +14664,11 @@
       <c r="AB135" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14778,7 +14874,11 @@
       <c r="AB137" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC137" s="4" t="inlineStr"/>
+      <c r="AC137" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -15497,7 +15597,11 @@
       <c r="AB144" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC144" s="4" t="inlineStr"/>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -16412,7 +16516,11 @@
       <c r="AB153" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC153" s="4" t="inlineStr"/>
+      <c r="AC153" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -17733,7 +17841,11 @@
       <c r="AB166" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC166" s="4" t="inlineStr"/>
+      <c r="AC166" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -18242,7 +18354,11 @@
       <c r="AB171" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC171" s="4" t="inlineStr"/>
+      <c r="AC171" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">

--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 119 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 114 clubs short</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2851,11 +2851,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P21" s="9" t="n">
-        <v>2</v>
+      <c r="P21" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6907,8 +6907,8 @@
       <c r="R60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="9" t="n">
-        <v>1</v>
+      <c r="S60" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T60" s="10" t="n">
         <v>1</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -7006,8 +7006,8 @@
       <c r="P61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" s="9" t="n">
-        <v>1</v>
+      <c r="Q61" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7222,8 +7222,8 @@
       <c r="R63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S63" s="9" t="n">
-        <v>1</v>
+      <c r="S63" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T63" s="9" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8346,8 +8346,8 @@
       <c r="Q74" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R74" s="9" t="n">
-        <v>1</v>
+      <c r="R74" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S74" s="10" t="n">
         <v>2</v>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>1</v>
@@ -8764,7 +8764,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9588,11 +9588,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P86" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q86" s="9" t="n">
-        <v>0</v>
+      <c r="P86" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -10978,15 +10978,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>7794</v>
+        <v>28675664</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Fluent Delivery In Public Speaking (FDIP) Club</t>
+          <t>Empowered Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -11000,10 +11000,10 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>0</v>
@@ -11038,8 +11038,8 @@
       <c r="S100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
@@ -11050,8 +11050,8 @@
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="10" t="n">
-        <v>6</v>
+      <c r="X100" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -11063,7 +11063,7 @@
         <v>1</v>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC100" s="4" t="inlineStr"/>
     </row>
@@ -11079,15 +11079,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28675664</v>
+        <v>7794</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Metro Manila South District Toastmasters Club</t>
+          <t>Fluent Delivery In Public Speaking (FDIP) Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11101,10 +11101,10 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
         <v>0</v>
@@ -11139,8 +11139,8 @@
       <c r="S101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T101" s="10" t="n">
-        <v>1</v>
+      <c r="T101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
@@ -11151,8 +11151,8 @@
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="9" t="n">
-        <v>3</v>
+      <c r="X101" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
         <v>1</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC101" s="4" t="inlineStr"/>
     </row>
@@ -13656,7 +13656,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13705,8 +13705,8 @@
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S126" s="9" t="n">
-        <v>1</v>
+      <c r="S126" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -15413,7 +15413,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15483,8 +15483,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15588,8 +15588,8 @@
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -15623,7 +15623,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15693,8 +15693,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15798,8 +15798,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15903,8 +15903,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -16785,7 +16785,7 @@
         </is>
       </c>
       <c r="P156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>0</v>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19654,8 +19654,8 @@
       <c r="Q184" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R184" s="9" t="n">
-        <v>1</v>
+      <c r="R184" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S184" s="10" t="n">
         <v>3</v>
@@ -20086,7 +20086,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -20350,13 +20350,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -20383,7 +20383,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -20449,7 +20449,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -20515,7 +20515,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -20779,7 +20779,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -20911,7 +20911,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -21208,7 +21208,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>

--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 56 clubs short</t>
         </is>
       </c>
     </row>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1829,8 +1829,8 @@
       <c r="S11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="9" t="n">
-        <v>0</v>
+      <c r="T11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="9" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -2030,8 +2030,8 @@
       <c r="P13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="9" t="n">
-        <v>0</v>
+      <c r="Q13" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
@@ -2049,7 +2049,7 @@
         <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>5</v>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3581,8 +3581,8 @@
       <c r="P28" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" s="9" t="n">
-        <v>0</v>
+      <c r="Q28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="S32" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" s="10" t="n">
         <v>1</v>
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4279,13 +4279,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -5115,13 +5115,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>6</v>
@@ -6048,13 +6048,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6191,8 +6191,8 @@
       <c r="S53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6599,8 +6599,8 @@
       <c r="S57" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T57" s="9" t="n">
-        <v>0</v>
+      <c r="T57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U57" s="9" t="n">
         <v>0</v>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -7288,13 +7288,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8411,13 +8411,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8455,8 +8455,8 @@
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="9" t="n">
-        <v>3</v>
+      <c r="V75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8611,13 +8611,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="P77" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q77" s="10" t="n">
         <v>2</v>
@@ -8647,7 +8647,7 @@
         <v>2</v>
       </c>
       <c r="S77" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T77" s="10" t="n">
         <v>1</v>
@@ -8659,7 +8659,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>4</v>
@@ -8821,13 +8821,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" s="10" t="n">
         <v>1</v>
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9859,17 +9859,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>60</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-60</v>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9903,11 +9903,11 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" s="9" t="n">
-        <v>0</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W89" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -11911,13 +11911,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>1</v>
       </c>
       <c r="U109" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V109" s="10" t="n">
         <v>4</v>
@@ -12769,7 +12769,7 @@
         <v>2</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12915,19 +12915,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28675727</v>
+        <v>7626109</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Albay Lawyers Toastmasters Club</t>
+          <t>Speak and Lead Cavite Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12941,13 +12941,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12967,17 +12967,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="9" t="n">
-        <v>0</v>
+      <c r="P119" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q119" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S119" s="9" t="n">
-        <v>0</v>
+      <c r="S119" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T119" s="9" t="n">
         <v>0</v>
@@ -12992,19 +12992,19 @@
         <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC119" s="4" t="inlineStr"/>
     </row>
@@ -13020,35 +13020,35 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28675465</v>
+        <v>28675727</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Kasanggayahan Toastmasters Club</t>
+          <t>Albay Lawyers Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F120" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G120" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I120" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="J120" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -13086,32 +13086,28 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="10" t="n">
-        <v>4</v>
+      <c r="V120" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="10" t="n">
-        <v>1</v>
+      <c r="Z120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC120" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13125,11 +13121,11 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>5001401</v>
+        <v>28675465</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Mayon Toastmasters Club</t>
+          <t>Kasanggayahan Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -13147,13 +13143,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13183,7 +13179,7 @@
         <v>0</v>
       </c>
       <c r="S121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T121" s="9" t="n">
         <v>0</v>
@@ -13195,7 +13191,7 @@
         <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>7</v>
@@ -13210,9 +13206,13 @@
         <v>1</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC121" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC121" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13226,15 +13226,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>7025040</v>
+        <v>5001401</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Naga Toastmasters Club</t>
+          <t>Mayon Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13275,31 +13275,31 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W122" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q122" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T122" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U122" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V122" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W122" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X122" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -13311,13 +13311,9 @@
         <v>1</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC122" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13331,15 +13327,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>28679811</v>
+        <v>7025040</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>SALUD BIKOLNON TOASTMASTERS CLUB</t>
+          <t>Naga Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13353,17 +13349,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -13380,45 +13376,49 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S123" s="9" t="n">
-        <v>0</v>
+      <c r="S123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T123" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
+      <c r="U123" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC123" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13428,19 +13428,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28677287</v>
+        <v>28679811</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>ADBGC TOASTMASTERS CLUB</t>
+          <t>SALUD BIKOLNON TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13454,17 +13454,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13481,7 +13481,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -13492,32 +13492,32 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="10" t="n">
-        <v>4</v>
+      <c r="V124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="10" t="n">
-        <v>1</v>
+      <c r="Z124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC124" s="4" t="inlineStr"/>
     </row>
@@ -13533,15 +13533,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>2833419</v>
+        <v>28677287</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>ADI Campus B Toastmasters Club</t>
+          <t>ADBGC TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13581,8 +13581,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P125" s="10" t="n">
-        <v>4</v>
+      <c r="P125" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -13591,10 +13591,10 @@
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T125" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U125" s="9" t="n">
         <v>0</v>
@@ -13606,7 +13606,7 @@
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13618,7 +13618,7 @@
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC125" s="4" t="inlineStr"/>
     </row>
@@ -13634,15 +13634,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7896316</v>
+        <v>2833419</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>ADPhils Encore Toastmasters Club</t>
+          <t>ADI Campus B Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13656,13 +13656,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13682,32 +13682,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P126" s="9" t="n">
-        <v>0</v>
+      <c r="P126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>1</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13719,7 +13719,7 @@
         <v>1</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC126" s="4" t="inlineStr"/>
     </row>
@@ -13735,15 +13735,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>7562429</v>
+        <v>7896316</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>ADPhils Toastmasters Club</t>
+          <t>ADPhils Encore Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13757,13 +13757,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13784,10 +13784,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q127" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q127" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13795,20 +13795,20 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U127" s="10" t="n">
-        <v>1</v>
+      <c r="T127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13820,13 +13820,9 @@
         <v>1</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC127" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AC127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -13840,15 +13836,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>3357121</v>
+        <v>7562429</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Dasmarinas City Toastmasters Club</t>
+          <t>ADPhils Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13862,13 +13858,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13888,33 +13884,33 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P128" s="10" t="n">
-        <v>6</v>
+      <c r="P128" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q128" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R128" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="T128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U128" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V128" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W128" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X128" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
@@ -13929,7 +13925,7 @@
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -13945,15 +13941,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>7626109</v>
+        <v>3357121</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Speak and Lead Cavite Toastmasters Club</t>
+          <t>Dasmarinas City Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13967,17 +13963,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L129" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13994,31 +13990,31 @@
         </is>
       </c>
       <c r="P129" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q129" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S129" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="W129" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -14030,9 +14026,13 @@
         <v>1</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -14585,13 +14585,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X135" s="9" t="n">
         <v>0</v>
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14690,13 +14690,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14734,8 +14734,8 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>3</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -15211,13 +15211,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="P141" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -15760,13 +15760,13 @@
         <v>0</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U146" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V146" s="9" t="n">
         <v>0</v>
@@ -17871,13 +17871,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -18586,17 +18586,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L174" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-16</v>
+      </c>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M174" s="8" t="n">
@@ -19749,7 +19749,7 @@
         <v>0</v>
       </c>
       <c r="S185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T185" s="9" t="n">
         <v>0</v>
@@ -19800,7 +19800,7 @@
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
@@ -19861,8 +19861,8 @@
       <c r="V186" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W186" s="9" t="n">
-        <v>3</v>
+      <c r="W186" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X186" s="10" t="n">
         <v>7</v>
@@ -20317,7 +20317,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -20416,13 +20416,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -20647,7 +20647,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -20746,7 +20746,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -20812,13 +20812,13 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -20827,7 +20827,7 @@
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -21007,16 +21007,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -21073,16 +21073,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -21142,7 +21142,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -21421,7 +21421,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -21505,7 +21505,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>

--- a/docs/d/75/inyear.xlsx
+++ b/docs/d/75/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$190</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 56 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC189"/>
+  <dimension ref="A1:AC190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -906,8 +906,8 @@
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>3</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1422,8 +1422,8 @@
       <c r="V7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W7" s="9" t="n">
-        <v>3</v>
+      <c r="W7" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X7" s="10" t="n">
         <v>4</v>
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1934,8 +1934,8 @@
       <c r="S12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="9" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -2048,8 +2048,8 @@
       <c r="V13" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>3</v>
+      <c r="W13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>5</v>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="P32" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q32" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R32" s="9" t="n">
-        <v>1</v>
+      <c r="R32" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S32" s="10" t="n">
         <v>3</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5353,8 +5353,8 @@
       <c r="Q45" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R45" s="9" t="n">
-        <v>1</v>
+      <c r="R45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S45" s="10" t="n">
         <v>2</v>
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -9859,13 +9859,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>60</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -10601,7 +10601,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>0</v>
@@ -11938,13 +11938,13 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q109" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S109" s="10" t="n">
         <v>3</v>
@@ -12455,7 +12455,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>1</v>
@@ -12739,13 +12739,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12876,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="10" t="n">
         <v>1</v>
@@ -13743,7 +13743,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13786,8 +13786,8 @@
       <c r="P127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" s="9" t="n">
-        <v>1</v>
+      <c r="Q127" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13858,13 +13858,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -14068,13 +14068,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -14118,8 +14118,8 @@
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="9" t="n">
-        <v>0</v>
+      <c r="X130" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -14223,8 +14223,8 @@
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="9" t="n">
-        <v>0</v>
+      <c r="X131" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -14274,13 +14274,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14319,13 +14319,13 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X132" s="9" t="n">
-        <v>0</v>
+      <c r="X132" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -14379,17 +14379,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L133" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -14427,10 +14427,10 @@
         <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X133" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -14534,8 +14534,8 @@
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="9" t="n">
-        <v>0</v>
+      <c r="X134" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14635,8 +14635,8 @@
       <c r="W135" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X135" s="9" t="n">
-        <v>0</v>
+      <c r="X135" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14740,8 +14740,8 @@
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="9" t="n">
-        <v>0</v>
+      <c r="X136" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -14791,13 +14791,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14841,8 +14841,8 @@
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X137" s="9" t="n">
-        <v>0</v>
+      <c r="X137" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14946,8 +14946,8 @@
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="9" t="n">
-        <v>0</v>
+      <c r="X138" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
@@ -15051,8 +15051,8 @@
       <c r="W139" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X139" s="9" t="n">
-        <v>0</v>
+      <c r="X139" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
@@ -15156,8 +15156,8 @@
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="9" t="n">
-        <v>0</v>
+      <c r="X140" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
@@ -15261,8 +15261,8 @@
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X141" s="9" t="n">
-        <v>0</v>
+      <c r="X141" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -15366,8 +15366,8 @@
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X142" s="9" t="n">
-        <v>0</v>
+      <c r="X142" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -15471,8 +15471,8 @@
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X143" s="9" t="n">
-        <v>0</v>
+      <c r="X143" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -15572,8 +15572,8 @@
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X144" s="9" t="n">
-        <v>0</v>
+      <c r="X144" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -15673,8 +15673,8 @@
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="9" t="n">
-        <v>0</v>
+      <c r="X145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
@@ -15774,8 +15774,8 @@
       <c r="W146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X146" s="9" t="n">
-        <v>0</v>
+      <c r="X146" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
@@ -15856,7 +15856,7 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -15879,8 +15879,8 @@
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="9" t="n">
-        <v>0</v>
+      <c r="X147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
@@ -15984,8 +15984,8 @@
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="9" t="n">
-        <v>0</v>
+      <c r="X148" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -16089,8 +16089,8 @@
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X149" s="9" t="n">
-        <v>0</v>
+      <c r="X149" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
@@ -16194,8 +16194,8 @@
       <c r="W150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X150" s="9" t="n">
-        <v>0</v>
+      <c r="X150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
@@ -16748,13 +16748,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>4</v>
       </c>
       <c r="W156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X156" s="10" t="n">
         <v>5</v>
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17160,17 +17160,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -17204,11 +17204,11 @@
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="9" t="n">
-        <v>0</v>
+      <c r="V160" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>6</v>
@@ -18770,15 +18770,15 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>3854</v>
+        <v>7808735</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>TM Club Of Davao Club</t>
+          <t>Sulu State College</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18792,25 +18792,25 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L176" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>12</v>
+      </c>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M176" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N176" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O176" s="7" t="inlineStr">
@@ -18836,26 +18836,26 @@
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X176" s="10" t="n">
+      <c r="V176" s="10" t="n">
         <v>4</v>
       </c>
+      <c r="W176" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="X176" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="Y176" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z176" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA176" s="10" t="n">
-        <v>1</v>
+      <c r="AA176" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB176" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC176" s="4" t="inlineStr"/>
     </row>
@@ -18867,15 +18867,15 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>1193122</v>
+        <v>3854</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Bulawan Toastmasters Club</t>
+          <t>TM Club Of Davao Club</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
@@ -18893,13 +18893,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18938,13 +18938,13 @@
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X177" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
@@ -18956,13 +18956,9 @@
         <v>1</v>
       </c>
       <c r="AB177" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC177" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -18976,15 +18972,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1480</v>
+        <v>1193122</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Davao Noontime Toastmasters Club</t>
+          <t>Bulawan Toastmasters Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18998,17 +18994,17 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L178" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M178" s="8" t="n">
@@ -19025,47 +19021,47 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q178" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q178" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R178" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S178" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T178" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U178" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V178" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W178" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X178" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA178" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB178" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="X178" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y178" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z178" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA178" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB178" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="AC178" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -19081,15 +19077,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>1360367</v>
+        <v>1480</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Palm City Toastmasters</t>
+          <t>Davao Noontime Toastmasters Club</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -19103,17 +19099,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L179" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
@@ -19130,31 +19126,31 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q179" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R179" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T179" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U179" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V179" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W179" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X179" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
@@ -19166,9 +19162,13 @@
         <v>1</v>
       </c>
       <c r="AB179" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC179" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC179" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -19182,11 +19182,11 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>9853</v>
+        <v>1360367</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Zamboanga Toastmasters Club</t>
+          <t>Palm City Toastmasters</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
@@ -19204,13 +19204,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -19254,20 +19254,20 @@
       <c r="W180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X180" s="9" t="n">
+      <c r="X180" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB180" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Y180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z180" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA180" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB180" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="AC180" s="4" t="inlineStr"/>
     </row>
@@ -19279,15 +19279,15 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>3789</v>
+        <v>9853</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Butuan Toastmasters Club</t>
+          <t>Zamboanga Toastmasters Club</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
@@ -19305,13 +19305,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -19355,8 +19355,8 @@
       <c r="W181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X181" s="10" t="n">
-        <v>4</v>
+      <c r="X181" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y181" s="9" t="n">
         <v>0</v>
@@ -19368,13 +19368,9 @@
         <v>1</v>
       </c>
       <c r="AB181" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC181" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -19388,11 +19384,11 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>28680330</v>
+        <v>3789</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>DACL GBS Speakers' Circle Toastmasters Club</t>
+          <t>Butuan Toastmasters Club</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
@@ -19410,17 +19406,17 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L182" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M182" s="8" t="n">
@@ -19455,7 +19451,7 @@
         <v>0</v>
       </c>
       <c r="V182" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
@@ -19473,9 +19469,13 @@
         <v>1</v>
       </c>
       <c r="AB182" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC182" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC182" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -19489,11 +19489,11 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>9238</v>
+        <v>28680330</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Davao Pag-Asa  Toastmasters Club</t>
+          <t>DACL GBS Speakers' Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
@@ -19511,17 +19511,17 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L183" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M183" s="8" t="n">
@@ -19556,13 +19556,13 @@
         <v>0</v>
       </c>
       <c r="V183" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W183" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X183" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y183" s="9" t="n">
         <v>0</v>
@@ -19574,7 +19574,7 @@
         <v>1</v>
       </c>
       <c r="AB183" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC183" s="4" t="inlineStr"/>
     </row>
@@ -19590,15 +19590,15 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>4933</v>
+        <v>9238</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Durian Toastmasters Club</t>
+          <t>Davao Pag-Asa  Toastmasters Club</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19612,13 +19612,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -19642,13 +19642,13 @@
         <v>0</v>
       </c>
       <c r="Q184" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R184" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S184" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T184" s="9" t="n">
         <v>0</v>
@@ -19656,14 +19656,14 @@
       <c r="U184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V184" s="10" t="n">
-        <v>4</v>
+      <c r="V184" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W184" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X184" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y184" s="9" t="n">
         <v>0</v>
@@ -19675,7 +19675,7 @@
         <v>1</v>
       </c>
       <c r="AB184" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC184" s="4" t="inlineStr"/>
     </row>
@@ -19691,11 +19691,11 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1450173</v>
+        <v>4933</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Downtown Butuan</t>
+          <t>Durian Toastmasters Club</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>0</v>
       </c>
       <c r="Q185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R185" s="9" t="n">
         <v>0</v>
@@ -19761,10 +19761,10 @@
         <v>4</v>
       </c>
       <c r="W185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X185" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y185" s="9" t="n">
         <v>0</v>
@@ -19776,7 +19776,7 @@
         <v>1</v>
       </c>
       <c r="AB185" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC185" s="4" t="inlineStr"/>
     </row>
@@ -19788,19 +19788,19 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>4494</v>
+        <v>1450173</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Cagayan De Oro Toastmasters Club</t>
+          <t>Toastmasters Club of Downtown Butuan</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19814,17 +19814,17 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L186" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L186" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M186" s="8" t="n">
@@ -19841,32 +19841,32 @@
         </is>
       </c>
       <c r="P186" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q186" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R186" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S186" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T186" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U186" s="10" t="n">
-        <v>1</v>
+      <c r="T186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V186" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W186" s="10" t="n">
+      <c r="W186" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X186" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X186" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y186" s="9" t="n">
         <v>0</v>
       </c>
@@ -19877,13 +19877,9 @@
         <v>1</v>
       </c>
       <c r="AB186" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC186" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -19897,11 +19893,11 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>1845318</v>
+        <v>4494</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Central CDO TMC</t>
+          <t>Cagayan De Oro Toastmasters Club</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
@@ -19919,13 +19915,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
@@ -19946,7 +19942,7 @@
         </is>
       </c>
       <c r="P187" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q187" s="10" t="n">
         <v>2</v>
@@ -19955,22 +19951,22 @@
         <v>2</v>
       </c>
       <c r="S187" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T187" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U187" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V187" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W187" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X187" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y187" s="9" t="n">
         <v>0</v>
@@ -19982,11 +19978,11 @@
         <v>1</v>
       </c>
       <c r="AB187" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC187" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -20002,15 +19998,15 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>7155</v>
+        <v>1845318</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Macajalar Bay Toastmasters Club</t>
+          <t>Central CDO TMC</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -20024,17 +20020,17 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L188" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M188" s="8" t="n">
@@ -20051,28 +20047,28 @@
         </is>
       </c>
       <c r="P188" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q188" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R188" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S188" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T188" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U188" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V188" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V188" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W188" s="9" t="n">
-        <v>0</v>
+      <c r="W188" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X188" s="10" t="n">
         <v>5</v>
@@ -20107,15 +20103,15 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>28680281</v>
+        <v>7155</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>PICPA CDO Toastmasters Club</t>
+          <t>Macajalar Bay Toastmasters Club</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -20129,17 +20125,17 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L189" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M189" s="8" t="n">
@@ -20155,11 +20151,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P189" s="9" t="n">
-        <v>0</v>
+      <c r="P189" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q189" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R189" s="9" t="n">
         <v>0</v>
@@ -20180,24 +20176,129 @@
         <v>0</v>
       </c>
       <c r="X189" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y189" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA189" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB189" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC189" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="n">
+        <v>28680281</v>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>PICPA CDO Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G190" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J190" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M190" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N190" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O190" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V190" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X190" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Y189" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z189" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA189" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB189" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC189" s="4" t="inlineStr"/>
+      <c r="Y190" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA190" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC190" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC189"/>
+  <autoFilter ref="A1:AC190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20284,7 +20385,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -20317,7 +20418,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -20350,13 +20451,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -20449,7 +20550,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -20548,7 +20649,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -21076,7 +21177,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -21124,7 +21225,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -21274,7 +21375,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -21289,7 +21390,7 @@
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -21403,25 +21504,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -21505,7 +21606,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
